--- a/DOCS/sprints/sprint-01/Tasks.xlsx
+++ b/DOCS/sprints/sprint-01/Tasks.xlsx
@@ -33,10 +33,10 @@
     <t>Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Esforço Ideal (Linha de Guia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esforço Real (O que falta)</t>
+    <t xml:space="preserve">Esforço Ideal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esforço Real</t>
   </si>
   <si>
     <t xml:space="preserve">DW01.1 </t>
@@ -223,8 +223,15 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -251,15 +258,27 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.099978637043366805"/>
+        <bgColor theme="2" tint="-0.099978637043366805"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor theme="4" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -286,6 +305,19 @@
       <left style="medium">
         <color theme="1"/>
       </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -358,7 +390,7 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color theme="1"/>
       </left>
       <right style="thin">
@@ -391,7 +423,7 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color theme="1"/>
       </right>
       <top style="thin">
@@ -406,13 +438,22 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color theme="1"/>
       </right>
       <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
         <color theme="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -421,74 +462,79 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="4" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -594,7 +640,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Esforço Ideal (Linha de Guia)</c:v>
+                  <c:v>Esforço Ideal</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -807,7 +853,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Esforço Real (O que falta)</c:v>
+                  <c:v>Esforço Real</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1013,11 +1059,11 @@
         </c:ser>
         <c:marker val="0"/>
         <c:smooth val="0"/>
-        <c:axId val="2140841523"/>
-        <c:axId val="2140841524"/>
+        <c:axId val="2140841541"/>
+        <c:axId val="2140841542"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2140841523"/>
+        <c:axId val="2140841541"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1061,7 +1107,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2140841524"/>
+        <c:crossAx val="2140841542"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1069,7 +1115,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2140841524"/>
+        <c:axId val="2140841542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1124,7 +1170,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2140841523"/>
+        <c:crossAx val="2140841541"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1179,8 +1225,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="13666610" y="201083"/>
-      <a:ext cx="5058833" cy="3026833"/>
+      <a:off x="13727905" y="250031"/>
+      <a:ext cx="5692774" cy="3405187"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -1815,26 +1861,26 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>169333</xdr:colOff>
+      <xdr:colOff>107156</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>24694</xdr:rowOff>
+      <xdr:rowOff>75405</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>373944</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>116416</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>300831</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>11905</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="384997362" name=""/>
+        <xdr:cNvPr id="925981217" name=""/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="13666610" y="201083"/>
-        <a:ext cx="5058833" cy="3026833"/>
+        <a:off x="13727905" y="250031"/>
+        <a:ext cx="5692774" cy="3405187"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2332,733 +2378,771 @@
     <col min="1" max="1" style="1" width="9.140625"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="57.68359375"/>
     <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="42.9609375"/>
-    <col bestFit="1" min="4" max="4" style="1" width="11.8828125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="13.57421875"/>
     <col customWidth="1" min="5" max="5" width="5.8515625"/>
     <col customWidth="1" min="6" max="6" style="2" width="11.7109375"/>
     <col customWidth="1" min="7" max="7" width="33.421875"/>
     <col customWidth="1" min="8" max="8" width="29.8515625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="1" t="s">
+    <row r="2" ht="15">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="F3" s="10">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="8">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9">
         <v>46108</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <v>81</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>81</v>
       </c>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3</v>
+      </c>
+      <c r="F4" s="12">
+        <v>46111</v>
+      </c>
+      <c r="G4" s="13">
+        <v>77.890000000000001</v>
+      </c>
+      <c r="H4" s="14">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" ht="15">
+      <c r="A5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8">
+        <v>5</v>
+      </c>
+      <c r="F5" s="12">
+        <v>46112</v>
+      </c>
+      <c r="G5" s="13">
+        <v>74.780000000000015</v>
+      </c>
+      <c r="H5" s="14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" ht="15">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8">
+        <v>5</v>
+      </c>
+      <c r="F6" s="12">
+        <v>46113</v>
+      </c>
+      <c r="G6" s="13">
+        <v>71.67000000000003</v>
+      </c>
+      <c r="H6" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="15">
+      <c r="A7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12">
+        <v>46114</v>
+      </c>
+      <c r="G7" s="13">
+        <v>68.560000000000045</v>
+      </c>
+      <c r="H7" s="15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" ht="15">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="8"/>
+      <c r="F8" s="12">
+        <v>46115</v>
+      </c>
+      <c r="G8" s="13">
+        <v>65.45000000000006</v>
+      </c>
+      <c r="H8" s="16">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" ht="15">
+      <c r="A9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="8">
+        <v>5</v>
+      </c>
+      <c r="F9" s="12">
+        <v>46118</v>
+      </c>
+      <c r="G9" s="13">
+        <v>62.340000000000067</v>
+      </c>
+      <c r="H9" s="16">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" ht="15">
+      <c r="A10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="8">
+        <v>3</v>
+      </c>
+      <c r="F10" s="12">
+        <v>46119</v>
+      </c>
+      <c r="G10" s="13">
+        <v>59.230000000000075</v>
+      </c>
+      <c r="H10" s="16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="15">
+      <c r="A11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="8">
+        <v>5</v>
+      </c>
+      <c r="F11" s="12">
+        <v>46120</v>
+      </c>
+      <c r="G11" s="13">
+        <v>56.12000000000009</v>
+      </c>
+      <c r="H11" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="15">
+      <c r="A12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="F12" s="12">
+        <v>46121</v>
+      </c>
+      <c r="G12" s="13">
+        <v>53.01000000000009</v>
+      </c>
+      <c r="H12" s="16">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" ht="15">
+      <c r="A13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="8">
+        <v>5</v>
+      </c>
+      <c r="F13" s="12">
+        <v>46122</v>
+      </c>
+      <c r="G13" s="13">
+        <v>49.900000000000105</v>
+      </c>
+      <c r="H13" s="16">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" ht="15">
+      <c r="A14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8">
         <v>3</v>
       </c>
-      <c r="F4" s="13">
-        <v>46111</v>
-      </c>
-      <c r="G4" s="14">
-        <v>77.890000000000001</v>
-      </c>
-      <c r="H4" s="15">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" ht="15">
-      <c r="A5" s="8" t="s">
+      <c r="F14" s="12">
+        <v>46125</v>
+      </c>
+      <c r="G14" s="13">
+        <v>46.790000000000113</v>
+      </c>
+      <c r="H14" s="16">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" ht="15">
+      <c r="A15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="8">
+        <v>8</v>
+      </c>
+      <c r="F15" s="12">
+        <v>46126</v>
+      </c>
+      <c r="G15" s="13">
+        <v>43.680000000000121</v>
+      </c>
+      <c r="H15" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" ht="15">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="8"/>
+      <c r="F16" s="12">
+        <v>46127</v>
+      </c>
+      <c r="G16" s="13">
+        <v>40.570000000000128</v>
+      </c>
+      <c r="H16" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="15">
+      <c r="A17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12">
+        <v>46128</v>
+      </c>
+      <c r="G17" s="13">
+        <v>37.460000000000143</v>
+      </c>
+      <c r="H17" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="15">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12">
+        <v>46129</v>
+      </c>
+      <c r="G18" s="13">
+        <v>34.350000000000151</v>
+      </c>
+      <c r="H18" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="15">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12">
+        <v>46132</v>
+      </c>
+      <c r="G19" s="13">
+        <v>31.240000000000158</v>
+      </c>
+      <c r="H19" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" ht="15">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="8"/>
+      <c r="F20" s="12">
+        <v>46133</v>
+      </c>
+      <c r="G20" s="13">
+        <v>28.130000000000166</v>
+      </c>
+      <c r="H20" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="15">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="8">
+        <v>3</v>
+      </c>
+      <c r="F21" s="12">
+        <v>46134</v>
+      </c>
+      <c r="G21" s="13">
+        <v>25.020000000000174</v>
+      </c>
+      <c r="H21" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="15">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="8"/>
+      <c r="F22" s="12">
+        <v>46135</v>
+      </c>
+      <c r="G22" s="13">
+        <v>21.910000000000188</v>
+      </c>
+      <c r="H22" s="16">
         <v>10</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1">
+    </row>
+    <row r="23" ht="15">
+      <c r="A23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="8">
         <v>3</v>
       </c>
-      <c r="F5" s="13">
-        <v>46112</v>
-      </c>
-      <c r="G5" s="11">
-        <v>74.780000000000015</v>
-      </c>
-      <c r="H5" s="15">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" ht="15">
-      <c r="A6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="F23" s="12">
+        <v>46136</v>
+      </c>
+      <c r="G23" s="13">
+        <v>18.780000000000001</v>
+      </c>
+      <c r="H23" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" ht="15">
+      <c r="A24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="8">
         <v>5</v>
       </c>
-      <c r="F6" s="13">
-        <v>46113</v>
-      </c>
-      <c r="G6" s="14">
-        <v>71.67000000000003</v>
-      </c>
-      <c r="H6" s="15">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" ht="15">
-      <c r="A7" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1">
-        <v>5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>46114</v>
-      </c>
-      <c r="G7" s="11">
-        <v>68.560000000000045</v>
-      </c>
-      <c r="H7" s="18">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
-      <c r="A8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="F24" s="12">
+        <v>46139</v>
+      </c>
+      <c r="G24" s="13">
+        <v>15.65</v>
+      </c>
+      <c r="H24" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" ht="15">
+      <c r="A25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="8">
         <v>2</v>
       </c>
-      <c r="F8" s="13">
-        <v>46115</v>
-      </c>
-      <c r="G8" s="11">
-        <v>65.45000000000006</v>
-      </c>
-      <c r="H8" s="19">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="F9" s="13">
-        <v>46118</v>
-      </c>
-      <c r="G9" s="14">
-        <v>62.340000000000067</v>
-      </c>
-      <c r="H9" s="19">
+      <c r="F25" s="12">
+        <v>46140</v>
+      </c>
+      <c r="G25" s="13">
+        <v>12.520000000000003</v>
+      </c>
+      <c r="H25" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" ht="15">
+      <c r="A26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2</v>
+      </c>
+      <c r="F26" s="12">
+        <v>46141</v>
+      </c>
+      <c r="G26" s="13">
+        <v>9.3900000000000041</v>
+      </c>
+      <c r="H26" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="15">
+      <c r="A27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2</v>
+      </c>
+      <c r="F27" s="12">
+        <v>46142</v>
+      </c>
+      <c r="G27" s="13">
+        <v>6.2600000000000051</v>
+      </c>
+      <c r="H27" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="15">
+      <c r="A28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2</v>
+      </c>
+      <c r="F28" s="12">
+        <v>46143</v>
+      </c>
+      <c r="G28" s="13">
+        <v>3.1300000000000061</v>
+      </c>
+      <c r="H28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15">
+      <c r="A29" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" ht="15">
-      <c r="A10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="F10" s="13">
-        <v>46119</v>
-      </c>
-      <c r="G10" s="11">
-        <v>59.230000000000075</v>
-      </c>
-      <c r="H10" s="19">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="15">
-      <c r="A11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="13">
-        <v>46120</v>
-      </c>
-      <c r="G11" s="14">
-        <v>56.12000000000009</v>
-      </c>
-      <c r="H11" s="19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" ht="15">
-      <c r="A12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="1">
-        <v>5</v>
-      </c>
-      <c r="F12" s="13">
-        <v>46121</v>
-      </c>
-      <c r="G12" s="11">
-        <v>53.01000000000009</v>
-      </c>
-      <c r="H12" s="19">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" ht="15">
-      <c r="A13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="1">
-        <v>8</v>
-      </c>
-      <c r="F13" s="13">
-        <v>46122</v>
-      </c>
-      <c r="G13" s="11">
-        <v>49.900000000000105</v>
-      </c>
-      <c r="H13" s="19">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="15">
-      <c r="A14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="1">
-        <v>5</v>
-      </c>
-      <c r="F14" s="13">
-        <v>46125</v>
-      </c>
-      <c r="G14" s="14">
-        <v>46.790000000000113</v>
-      </c>
-      <c r="H14" s="19">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" ht="15">
-      <c r="A15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46126</v>
-      </c>
-      <c r="G15" s="11">
-        <v>43.680000000000121</v>
-      </c>
-      <c r="H15" s="19">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" ht="15">
-      <c r="A16" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="1">
-        <v>8</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46127</v>
-      </c>
-      <c r="G16" s="14">
-        <v>40.570000000000128</v>
-      </c>
-      <c r="H16" s="19">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" ht="15">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="F17" s="13">
-        <v>46128</v>
-      </c>
-      <c r="G17" s="11">
-        <v>37.460000000000143</v>
-      </c>
-      <c r="H17" s="19">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" ht="15">
-      <c r="A18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="13">
-        <v>46129</v>
-      </c>
-      <c r="G18" s="11">
-        <v>34.350000000000151</v>
-      </c>
-      <c r="H18" s="19">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" ht="15">
-      <c r="A19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="13">
-        <v>46132</v>
-      </c>
-      <c r="G19" s="14">
-        <v>31.240000000000158</v>
-      </c>
-      <c r="H19" s="19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" ht="15">
-      <c r="A20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="13">
-        <v>46133</v>
-      </c>
-      <c r="G20" s="11">
-        <v>28.130000000000166</v>
-      </c>
-      <c r="H20" s="19">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" ht="15">
-      <c r="A21" s="8"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="F21" s="13">
-        <v>46134</v>
-      </c>
-      <c r="G21" s="14">
-        <v>25.020000000000174</v>
-      </c>
-      <c r="H21" s="19">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" ht="15">
-      <c r="A22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="1">
-        <v>3</v>
-      </c>
-      <c r="F22" s="13">
-        <v>46135</v>
-      </c>
-      <c r="G22" s="11">
-        <v>21.910000000000188</v>
-      </c>
-      <c r="H22" s="19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" ht="15">
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="F23" s="13">
-        <v>46136</v>
-      </c>
-      <c r="G23" s="11">
-        <v>18.780000000000001</v>
-      </c>
-      <c r="H23" s="19">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="15">
-      <c r="A24" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="F24" s="13">
-        <v>46139</v>
-      </c>
-      <c r="G24" s="14">
-        <v>15.65</v>
-      </c>
-      <c r="H24" s="19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" ht="15">
-      <c r="A25" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="1">
-        <v>5</v>
-      </c>
-      <c r="F25" s="13">
-        <v>46140</v>
-      </c>
-      <c r="G25" s="11">
-        <v>12.520000000000003</v>
-      </c>
-      <c r="H25" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" ht="15">
-      <c r="A26" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D29" s="8">
+        <v>2</v>
+      </c>
+      <c r="F29" s="18">
+        <v>46146</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="15">
+      <c r="A30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D30" s="8">
         <v>2</v>
       </c>
-      <c r="F26" s="13">
-        <v>46141</v>
-      </c>
-      <c r="G26" s="14">
-        <v>9.3900000000000041</v>
-      </c>
-      <c r="H26" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" ht="15">
-      <c r="A27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="13">
-        <v>46142</v>
-      </c>
-      <c r="G27" s="11">
-        <v>6.2600000000000051</v>
-      </c>
-      <c r="H27" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15">
-      <c r="A28" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="13">
-        <v>46143</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3.1300000000000061</v>
-      </c>
-      <c r="H28" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15">
-      <c r="A29" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="F29" s="25">
-        <v>46146</v>
-      </c>
-      <c r="G29" s="11">
-        <v>0</v>
-      </c>
-      <c r="H29" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15">
-      <c r="A30" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
     </row>
     <row r="31" ht="15">
-      <c r="A31" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="F31" s="2"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="23">
+        <f>SUM(D3:D30)</f>
+        <v>81</v>
+      </c>
     </row>
     <row r="32" ht="15">
-      <c r="A32" s="1"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="24"/>
       <c r="D32" s="1"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="9"/>
     </row>
     <row r="33" ht="15">
-      <c r="D33" s="1">
-        <f>SUM(D4:D31)</f>
-        <v>81</v>
-      </c>
-      <c r="G33" s="26"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="1"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
     </row>
     <row r="34" ht="15">
-      <c r="A34" s="1"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="9"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
     </row>
     <row r="35" ht="15">
       <c r="A35" s="1"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="9"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
     </row>
     <row r="36" ht="15">
       <c r="A36" s="1"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="9"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
     </row>
     <row r="37" ht="15">
-      <c r="G37" s="26"/>
-      <c r="H37" s="9"/>
+      <c r="A37" s="1"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" ht="15">
-      <c r="F38" s="2"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="9"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
     </row>
     <row r="39" ht="15">
-      <c r="A39" s="1"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="9"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" ht="15">
-      <c r="A40" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="1"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
     </row>
     <row r="41" ht="15">
       <c r="A41" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="26"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+    </row>
+    <row r="42" ht="15">
+      <c r="A42" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B42" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="G41" s="26"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" ht="15">
-      <c r="G42" s="26"/>
-      <c r="H42" s="9"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
     </row>
     <row r="43" ht="15">
-      <c r="G43" s="29"/>
-      <c r="H43" s="28"/>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="F44" s="2"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+    </row>
+    <row r="44" ht="15">
+      <c r="F44" s="26"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="F45" s="26"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="24"/>
+      <c r="C46" s="24"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
+      <c r="A47" s="24"/>
+      <c r="C47" s="24"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="24"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="24"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="24"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
+      <c r="A50" s="24"/>
+      <c r="C50" s="24"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="24"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="24"/>
+      <c r="C52" s="24"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="24"/>
+      <c r="C53" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
